--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ALL Project\Bikin keterangan Resi\ResiText-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E71472-7A4F-4D74-B477-9A3FAC1EFA45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C5AA8C-49C5-44E5-B8F8-E7E54133C487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2282" yWindow="2282" windowWidth="19563" windowHeight="10162" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,74 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="22">
-  <si>
-    <t>READY</t>
-  </si>
-  <si>
-    <t>3 ODOL MARVIS SILVER</t>
-  </si>
-  <si>
-    <t>6 ELIPS KOMPLIT</t>
-  </si>
-  <si>
-    <t>1 HB M56 + 1 HB GLOSSY</t>
-  </si>
-  <si>
-    <t>3 COLLAGEN COFFEE</t>
-  </si>
-  <si>
-    <t>3 ODOL MARVIS SILVER+3 COLLAGEN COFFEE</t>
-  </si>
-  <si>
-    <t>6 ODOL MARVIS SILVER+3 COLLAGEN COFFEE</t>
-  </si>
-  <si>
-    <t>1 PAKET ISI 4 BRA RENDA HITAM ABU ARMY MERAH 38 + 1 SET CD ACAK</t>
-  </si>
-  <si>
-    <t>1 SMARTWATCH Y13 HITAM + 1 SMARTBAND M8</t>
-  </si>
-  <si>
-    <t>FAMI</t>
-  </si>
-  <si>
-    <t>L25B020T6S</t>
-  </si>
-  <si>
-    <t>L25B020T6T</t>
-  </si>
-  <si>
-    <t>L25B020T6U</t>
-  </si>
-  <si>
-    <t>L25B020T6V</t>
-  </si>
-  <si>
-    <t>L25B020T6W</t>
-  </si>
-  <si>
-    <t>L25B020T6X</t>
-  </si>
-  <si>
-    <t>L25B020T6Y</t>
-  </si>
-  <si>
-    <t>L25B020T6Z</t>
-  </si>
-  <si>
-    <t>L25B020T70</t>
-  </si>
-  <si>
-    <t>L25B020T71</t>
-  </si>
-  <si>
-    <t>L25B020T72</t>
-  </si>
-  <si>
-    <t>L25B020T73</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -790,257 +723,113 @@
     <col min="1" max="1" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="31">
-        <v>450</v>
-      </c>
+    <row r="1" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="30"/>
+      <c r="B1" s="31"/>
       <c r="C1" s="32"/>
-      <c r="D1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="35">
-        <v>15320310307</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="28.55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="29">
-        <v>450</v>
-      </c>
+      <c r="D1" s="23"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="35"/>
+    </row>
+    <row r="2" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="28"/>
+      <c r="B2" s="29"/>
       <c r="C2" s="18"/>
-      <c r="D2" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="37">
-        <v>15320310305</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="28.55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="29">
-        <v>390</v>
-      </c>
+      <c r="D2" s="26"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="37"/>
+    </row>
+    <row r="3" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="18"/>
-      <c r="D3" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="37">
-        <v>15320310304</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="28.55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="29">
-        <v>390</v>
-      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="37"/>
+    </row>
+    <row r="4" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
       <c r="C4" s="18"/>
-      <c r="D4" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="37">
-        <v>15320309533</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="28.55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="29">
-        <v>390</v>
-      </c>
+      <c r="D4" s="26"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="37"/>
+    </row>
+    <row r="5" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29"/>
       <c r="C5" s="18"/>
-      <c r="D5" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="37">
-        <v>15320309534</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="28.55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="29">
-        <v>390</v>
-      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="37"/>
+    </row>
+    <row r="6" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="28"/>
+      <c r="B6" s="29"/>
       <c r="C6" s="18"/>
-      <c r="D6" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="37">
-        <v>15320309531</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="28.55" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="29">
-        <v>390</v>
-      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="37"/>
+    </row>
+    <row r="7" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
       <c r="C7" s="18"/>
-      <c r="D7" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="37">
-        <v>15320309529</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="33.299999999999997" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="29">
-        <v>840</v>
-      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="18"/>
-      <c r="D8" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="37">
-        <v>15320310303</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="33.299999999999997" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="29">
-        <v>1230</v>
-      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="37"/>
+    </row>
+    <row r="9" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="28"/>
+      <c r="B9" s="29"/>
       <c r="C9" s="18"/>
-      <c r="D9" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="37">
-        <v>15320309535</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="33.299999999999997" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="25">
-        <v>580</v>
-      </c>
+      <c r="D9" s="26"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="37"/>
+    </row>
+    <row r="10" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="33"/>
-      <c r="D10" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="37">
-        <v>15320310306</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="49.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="25">
-        <v>490</v>
-      </c>
+      <c r="D10" s="26"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="37"/>
+    </row>
+    <row r="11" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25"/>
       <c r="C11" s="20"/>
-      <c r="D11" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="37">
-        <v>15320309530</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="49.6" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="25">
-        <v>499</v>
-      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="37"/>
+    </row>
+    <row r="12" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25"/>
       <c r="C12" s="20"/>
-      <c r="D12" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="39">
-        <v>15320309532</v>
-      </c>
+      <c r="D12" s="26"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="39"/>
     </row>
     <row r="13" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="24"/>

--- a/input.xlsx
+++ b/input.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ALL Project\Bikin keterangan Resi\ResiText-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C5AA8C-49C5-44E5-B8F8-E7E54133C487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DF17AF-525D-4D9A-9DA4-2EEA2039C702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2282" yWindow="2282" windowWidth="19563" windowHeight="10162" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,10 +22,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>

--- a/input.xlsx
+++ b/input.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ALL Project\Bikin keterangan Resi\ResiText-App\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All Project\ResiText\ResiText-App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61DF17AF-525D-4D9A-9DA4-2EEA2039C702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2282" yWindow="2282" windowWidth="19563" windowHeight="10162" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="19560" windowHeight="10166"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,9 +23,71 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="19">
+  <si>
+    <t>xdvxdvxd</t>
+  </si>
+  <si>
+    <t>awdwadwad</t>
+  </si>
+  <si>
+    <t>HEADSET ANTING X22</t>
+  </si>
+  <si>
+    <t>N18496379346</t>
+  </si>
+  <si>
+    <t>N18496399296</t>
+  </si>
+  <si>
+    <t>N18496409037</t>
+  </si>
+  <si>
+    <t>N18496418996</t>
+  </si>
+  <si>
+    <t>N18496429024</t>
+  </si>
+  <si>
+    <t>N18496449162</t>
+  </si>
+  <si>
+    <t>N18496459094</t>
+  </si>
+  <si>
+    <t>N18496469101</t>
+  </si>
+  <si>
+    <t>N18496478875</t>
+  </si>
+  <si>
+    <t>N18496488810</t>
+  </si>
+  <si>
+    <t>N18496508817</t>
+  </si>
+  <si>
+    <t>N18496518940</t>
+  </si>
+  <si>
+    <t>N18496528908</t>
+  </si>
+  <si>
+    <t>N18496548915</t>
+  </si>
+  <si>
+    <t>N18496558656</t>
+  </si>
+  <si>
+    <t>N18496575441</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,19 +167,6 @@
       <name val="Lato"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Lato"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -158,27 +206,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -226,158 +259,101 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="10" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="16" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -712,608 +688,734 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G194"/>
-  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="34"/>
+    <row r="1" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A1" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="29"/>
       <c r="F1" s="16"/>
-      <c r="G1" s="35"/>
-    </row>
-    <row r="2" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="36"/>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A2" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="29"/>
       <c r="F2" s="20"/>
-      <c r="G2" s="37"/>
-    </row>
-    <row r="3" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="36"/>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A3" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="29"/>
       <c r="F3" s="20"/>
-      <c r="G3" s="37"/>
-    </row>
-    <row r="4" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="36"/>
+      <c r="G3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A4" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="25"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="20"/>
-      <c r="G4" s="37"/>
-    </row>
-    <row r="5" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="36"/>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A5" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="25"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="20"/>
-      <c r="G5" s="37"/>
-    </row>
-    <row r="6" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="36"/>
+      <c r="G5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A6" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="25"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="20"/>
-      <c r="G6" s="37"/>
-    </row>
-    <row r="7" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="36"/>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A7" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="20"/>
-      <c r="G7" s="37"/>
-    </row>
-    <row r="8" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="36"/>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A8" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="20"/>
-      <c r="G8" s="37"/>
-    </row>
-    <row r="9" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="28"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="36"/>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A9" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="25"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="20"/>
-      <c r="G9" s="37"/>
-    </row>
-    <row r="10" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="26"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="37"/>
-    </row>
-    <row r="11" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="36"/>
+      <c r="G9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A10" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="25"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="30"/>
+      <c r="G10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A11" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="25"/>
+      <c r="E11" s="29"/>
       <c r="F11" s="20"/>
-      <c r="G11" s="37"/>
-    </row>
-    <row r="12" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="36"/>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A12" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B12" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="25"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="20"/>
-      <c r="G12" s="39"/>
-    </row>
-    <row r="13" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="27"/>
+      <c r="G12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A13" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="21"/>
-    </row>
-    <row r="14" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="27"/>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A14" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="25"/>
+      <c r="E14" s="26"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="21"/>
-    </row>
-    <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="28"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="27"/>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A15" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="25"/>
+      <c r="E15" s="26"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="21"/>
-    </row>
-    <row r="16" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="28"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="27"/>
+      <c r="G15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="25.3" thickBot="1">
+      <c r="A16" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="25"/>
+      <c r="E16" s="26"/>
       <c r="F16" s="19"/>
-      <c r="G16" s="21"/>
-    </row>
-    <row r="17" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29"/>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A17" s="27"/>
+      <c r="B17" s="28"/>
       <c r="C17" s="18"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="27"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="26"/>
       <c r="F17" s="19"/>
       <c r="G17" s="21"/>
     </row>
-    <row r="18" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="28"/>
-      <c r="B18" s="29"/>
+    <row r="18" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28"/>
       <c r="C18" s="18"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="27"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="26"/>
       <c r="F18" s="19"/>
       <c r="G18" s="21"/>
     </row>
-    <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28"/>
-      <c r="B19" s="29"/>
+    <row r="19" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28"/>
       <c r="C19" s="18"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="27"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="26"/>
       <c r="F19" s="19"/>
       <c r="G19" s="21"/>
     </row>
-    <row r="20" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="28"/>
-      <c r="B20" s="29"/>
+    <row r="20" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="18"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="27"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="26"/>
       <c r="F20" s="19"/>
       <c r="G20" s="21"/>
     </row>
-    <row r="21" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="28"/>
-      <c r="B21" s="29"/>
+    <row r="21" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28"/>
       <c r="C21" s="18"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="27"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="26"/>
       <c r="F21" s="19"/>
       <c r="G21" s="21"/>
     </row>
-    <row r="22" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="28"/>
-      <c r="B22" s="29"/>
+    <row r="22" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28"/>
       <c r="C22" s="18"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="27"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
       <c r="F22" s="19"/>
       <c r="G22" s="21"/>
     </row>
-    <row r="23" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29"/>
+    <row r="23" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28"/>
       <c r="C23" s="18"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="27"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="26"/>
       <c r="F23" s="19"/>
       <c r="G23" s="21"/>
     </row>
-    <row r="24" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="28"/>
-      <c r="B24" s="29"/>
+    <row r="24" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28"/>
       <c r="C24" s="18"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="27"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="26"/>
       <c r="F24" s="19"/>
       <c r="G24" s="21"/>
     </row>
-    <row r="25" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="28"/>
-      <c r="B25" s="29"/>
+    <row r="25" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A25" s="27"/>
+      <c r="B25" s="28"/>
       <c r="C25" s="18"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="27"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="26"/>
       <c r="F25" s="19"/>
       <c r="G25" s="21"/>
     </row>
-    <row r="26" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="28"/>
-      <c r="B26" s="29"/>
+    <row r="26" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A26" s="27"/>
+      <c r="B26" s="28"/>
       <c r="C26" s="18"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="27"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="26"/>
       <c r="F26" s="19"/>
       <c r="G26" s="21"/>
     </row>
-    <row r="27" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28"/>
-      <c r="B27" s="29"/>
+    <row r="27" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A27" s="27"/>
+      <c r="B27" s="28"/>
       <c r="C27" s="18"/>
-      <c r="D27" s="26"/>
-      <c r="E27" s="27"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="26"/>
       <c r="F27" s="19"/>
       <c r="G27" s="21"/>
     </row>
-    <row r="28" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="28"/>
-      <c r="B28" s="29"/>
+    <row r="28" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A28" s="27"/>
+      <c r="B28" s="28"/>
       <c r="C28" s="18"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="27"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
       <c r="F28" s="19"/>
       <c r="G28" s="21"/>
     </row>
-    <row r="29" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="28"/>
-      <c r="B29" s="29"/>
+    <row r="29" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A29" s="27"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="18"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="27"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="26"/>
       <c r="F29" s="19"/>
       <c r="G29" s="21"/>
     </row>
-    <row r="30" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="28"/>
-      <c r="B30" s="29"/>
+    <row r="30" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A30" s="27"/>
+      <c r="B30" s="28"/>
       <c r="C30" s="18"/>
-      <c r="D30" s="26"/>
-      <c r="E30" s="27"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="26"/>
       <c r="F30" s="19"/>
       <c r="G30" s="21"/>
     </row>
-    <row r="31" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="28"/>
-      <c r="B31" s="29"/>
+    <row r="31" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A31" s="27"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="18"/>
-      <c r="D31" s="26"/>
-      <c r="E31" s="27"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="26"/>
       <c r="F31" s="19"/>
       <c r="G31" s="21"/>
     </row>
-    <row r="32" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="28"/>
-      <c r="B32" s="29"/>
+    <row r="32" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A32" s="27"/>
+      <c r="B32" s="28"/>
       <c r="C32" s="18"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="27"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
       <c r="F32" s="19"/>
       <c r="G32" s="21"/>
     </row>
-    <row r="33" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="28"/>
-      <c r="B33" s="29"/>
+    <row r="33" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A33" s="27"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="18"/>
-      <c r="D33" s="26"/>
-      <c r="E33" s="27"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="26"/>
       <c r="F33" s="19"/>
       <c r="G33" s="21"/>
     </row>
-    <row r="34" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="28"/>
-      <c r="B34" s="29"/>
+    <row r="34" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A34" s="27"/>
+      <c r="B34" s="28"/>
       <c r="C34" s="18"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="27"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
       <c r="F34" s="19"/>
       <c r="G34" s="21"/>
     </row>
-    <row r="35" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="28"/>
-      <c r="B35" s="29"/>
+    <row r="35" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A35" s="27"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="18"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="27"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="26"/>
       <c r="F35" s="19"/>
       <c r="G35" s="21"/>
     </row>
-    <row r="36" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="28"/>
-      <c r="B36" s="29"/>
+    <row r="36" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A36" s="27"/>
+      <c r="B36" s="28"/>
       <c r="C36" s="18"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="27"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="26"/>
       <c r="F36" s="19"/>
       <c r="G36" s="21"/>
     </row>
-    <row r="37" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="28"/>
-      <c r="B37" s="29"/>
+    <row r="37" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A37" s="27"/>
+      <c r="B37" s="28"/>
       <c r="C37" s="18"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="27"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="26"/>
       <c r="F37" s="19"/>
       <c r="G37" s="21"/>
     </row>
-    <row r="38" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="28"/>
-      <c r="B38" s="29"/>
+    <row r="38" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A38" s="27"/>
+      <c r="B38" s="28"/>
       <c r="C38" s="18"/>
-      <c r="D38" s="26"/>
-      <c r="E38" s="27"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="26"/>
       <c r="F38" s="19"/>
       <c r="G38" s="21"/>
     </row>
-    <row r="39" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="28"/>
-      <c r="B39" s="29"/>
+    <row r="39" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A39" s="27"/>
+      <c r="B39" s="28"/>
       <c r="C39" s="18"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="27"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="26"/>
       <c r="F39" s="19"/>
       <c r="G39" s="21"/>
     </row>
-    <row r="40" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="28"/>
-      <c r="B40" s="29"/>
+    <row r="40" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A40" s="27"/>
+      <c r="B40" s="28"/>
       <c r="C40" s="18"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="27"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="26"/>
       <c r="F40" s="19"/>
       <c r="G40" s="21"/>
     </row>
-    <row r="41" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="28"/>
-      <c r="B41" s="29"/>
+    <row r="41" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A41" s="27"/>
+      <c r="B41" s="28"/>
       <c r="C41" s="18"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="27"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="26"/>
       <c r="F41" s="19"/>
       <c r="G41" s="21"/>
     </row>
-    <row r="42" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="28"/>
-      <c r="B42" s="29"/>
+    <row r="42" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A42" s="27"/>
+      <c r="B42" s="28"/>
       <c r="C42" s="18"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="27"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="26"/>
       <c r="F42" s="19"/>
       <c r="G42" s="21"/>
     </row>
-    <row r="43" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="28"/>
-      <c r="B43" s="29"/>
+    <row r="43" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A43" s="27"/>
+      <c r="B43" s="28"/>
       <c r="C43" s="18"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="27"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="26"/>
       <c r="F43" s="19"/>
       <c r="G43" s="21"/>
     </row>
-    <row r="44" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="28"/>
-      <c r="B44" s="29"/>
+    <row r="44" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A44" s="27"/>
+      <c r="B44" s="28"/>
       <c r="C44" s="18"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="27"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="26"/>
       <c r="F44" s="19"/>
       <c r="G44" s="21"/>
     </row>
-    <row r="45" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="28"/>
-      <c r="B45" s="29"/>
+    <row r="45" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A45" s="27"/>
+      <c r="B45" s="28"/>
       <c r="C45" s="18"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="27"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="26"/>
       <c r="F45" s="19"/>
       <c r="G45" s="21"/>
     </row>
-    <row r="46" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="28"/>
-      <c r="B46" s="29"/>
+    <row r="46" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A46" s="27"/>
+      <c r="B46" s="28"/>
       <c r="C46" s="18"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="27"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="26"/>
       <c r="F46" s="19"/>
       <c r="G46" s="21"/>
     </row>
-    <row r="47" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="28"/>
-      <c r="B47" s="29"/>
+    <row r="47" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A47" s="27"/>
+      <c r="B47" s="28"/>
       <c r="C47" s="18"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="27"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="26"/>
       <c r="F47" s="19"/>
       <c r="G47" s="21"/>
     </row>
-    <row r="48" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="28"/>
-      <c r="B48" s="29"/>
+    <row r="48" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A48" s="27"/>
+      <c r="B48" s="28"/>
       <c r="C48" s="18"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="27"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="26"/>
       <c r="F48" s="19"/>
       <c r="G48" s="21"/>
     </row>
-    <row r="49" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="28"/>
-      <c r="B49" s="29"/>
+    <row r="49" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A49" s="27"/>
+      <c r="B49" s="28"/>
       <c r="C49" s="18"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="27"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="26"/>
       <c r="F49" s="19"/>
       <c r="G49" s="21"/>
     </row>
-    <row r="50" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="28"/>
-      <c r="B50" s="29"/>
+    <row r="50" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A50" s="27"/>
+      <c r="B50" s="28"/>
       <c r="C50" s="18"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="27"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="26"/>
       <c r="F50" s="19"/>
       <c r="G50" s="21"/>
     </row>
-    <row r="51" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="24"/>
-      <c r="B51" s="25"/>
+    <row r="51" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A51" s="23"/>
+      <c r="B51" s="24"/>
       <c r="C51" s="20"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="27"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="26"/>
       <c r="F51" s="19"/>
       <c r="G51" s="21"/>
     </row>
-    <row r="52" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="28"/>
-      <c r="B52" s="29"/>
+    <row r="52" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A52" s="27"/>
+      <c r="B52" s="28"/>
       <c r="C52" s="18"/>
-      <c r="D52" s="26"/>
-      <c r="E52" s="27"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="26"/>
       <c r="F52" s="19"/>
       <c r="G52" s="21"/>
     </row>
-    <row r="53" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="28"/>
-      <c r="B53" s="29"/>
+    <row r="53" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A53" s="27"/>
+      <c r="B53" s="28"/>
       <c r="C53" s="18"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="27"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="26"/>
       <c r="F53" s="19"/>
       <c r="G53" s="21"/>
     </row>
-    <row r="54" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="28"/>
-      <c r="B54" s="29"/>
+    <row r="54" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A54" s="27"/>
+      <c r="B54" s="28"/>
       <c r="C54" s="18"/>
-      <c r="D54" s="26"/>
-      <c r="E54" s="27"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="26"/>
       <c r="F54" s="19"/>
       <c r="G54" s="20"/>
     </row>
-    <row r="55" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="28"/>
-      <c r="B55" s="29"/>
+    <row r="55" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A55" s="27"/>
+      <c r="B55" s="28"/>
       <c r="C55" s="18"/>
-      <c r="D55" s="26"/>
-      <c r="E55" s="27"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="26"/>
       <c r="F55" s="19"/>
       <c r="G55" s="20"/>
     </row>
-    <row r="56" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="24"/>
-      <c r="B56" s="25"/>
+    <row r="56" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A56" s="23"/>
+      <c r="B56" s="24"/>
       <c r="C56" s="20"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="27"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="26"/>
       <c r="F56" s="19"/>
       <c r="G56" s="21"/>
     </row>
-    <row r="57" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="28"/>
-      <c r="B57" s="29"/>
+    <row r="57" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A57" s="27"/>
+      <c r="B57" s="28"/>
       <c r="C57" s="18"/>
-      <c r="D57" s="26"/>
-      <c r="E57" s="27"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="26"/>
       <c r="F57" s="19"/>
       <c r="G57" s="20"/>
     </row>
-    <row r="58" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="24"/>
-      <c r="B58" s="25"/>
+    <row r="58" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A58" s="23"/>
+      <c r="B58" s="24"/>
       <c r="C58" s="20"/>
-      <c r="D58" s="26"/>
-      <c r="E58" s="27"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="26"/>
       <c r="F58" s="19"/>
       <c r="G58" s="21"/>
     </row>
-    <row r="59" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="24"/>
-      <c r="B59" s="25"/>
+    <row r="59" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A59" s="23"/>
+      <c r="B59" s="24"/>
       <c r="C59" s="20"/>
-      <c r="D59" s="26"/>
-      <c r="E59" s="27"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="26"/>
       <c r="F59" s="19"/>
       <c r="G59" s="21"/>
     </row>
-    <row r="60" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="24"/>
-      <c r="B60" s="25"/>
+    <row r="60" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A60" s="23"/>
+      <c r="B60" s="24"/>
       <c r="C60" s="20"/>
-      <c r="D60" s="26"/>
-      <c r="E60" s="27"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="26"/>
       <c r="F60" s="19"/>
       <c r="G60" s="21"/>
     </row>
-    <row r="61" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="28"/>
-      <c r="B61" s="29"/>
+    <row r="61" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A61" s="27"/>
+      <c r="B61" s="28"/>
       <c r="C61" s="18"/>
-      <c r="D61" s="26"/>
-      <c r="E61" s="27"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="26"/>
       <c r="F61" s="19"/>
       <c r="G61" s="21"/>
     </row>
-    <row r="62" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="28"/>
-      <c r="B62" s="29"/>
+    <row r="62" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A62" s="27"/>
+      <c r="B62" s="28"/>
       <c r="C62" s="18"/>
-      <c r="D62" s="26"/>
-      <c r="E62" s="27"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="26"/>
       <c r="F62" s="19"/>
       <c r="G62" s="21"/>
     </row>
-    <row r="63" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="28"/>
-      <c r="B63" s="29"/>
+    <row r="63" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A63" s="27"/>
+      <c r="B63" s="28"/>
       <c r="C63" s="18"/>
-      <c r="D63" s="26"/>
-      <c r="E63" s="27"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="26"/>
       <c r="F63" s="19"/>
       <c r="G63" s="20"/>
     </row>
-    <row r="64" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="24"/>
-      <c r="B64" s="25"/>
+    <row r="64" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A64" s="23"/>
+      <c r="B64" s="24"/>
       <c r="C64" s="20"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="27"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="26"/>
       <c r="F64" s="19"/>
       <c r="G64" s="20"/>
     </row>
-    <row r="65" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="24"/>
-      <c r="B65" s="25"/>
+    <row r="65" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A65" s="23"/>
+      <c r="B65" s="24"/>
       <c r="C65" s="20"/>
-      <c r="D65" s="26"/>
-      <c r="E65" s="27"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="26"/>
       <c r="F65" s="19"/>
       <c r="G65" s="20"/>
     </row>
-    <row r="66" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="28"/>
-      <c r="B66" s="29"/>
+    <row r="66" spans="1:7" ht="14.6" thickBot="1">
+      <c r="A66" s="27"/>
+      <c r="B66" s="28"/>
       <c r="C66" s="18"/>
-      <c r="D66" s="26"/>
-      <c r="E66" s="27"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="26"/>
       <c r="F66" s="19"/>
       <c r="G66" s="20"/>
     </row>
-    <row r="67" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:7" ht="14.6" thickBot="1">
       <c r="A67" s="14"/>
       <c r="B67" s="17"/>
       <c r="C67" s="20"/>
@@ -1322,7 +1424,7 @@
       <c r="F67" s="19"/>
       <c r="G67" s="20"/>
     </row>
-    <row r="68" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:7" ht="14.6" thickBot="1">
       <c r="A68" s="14"/>
       <c r="B68" s="17"/>
       <c r="C68" s="18"/>
@@ -1331,7 +1433,7 @@
       <c r="F68" s="19"/>
       <c r="G68" s="21"/>
     </row>
-    <row r="69" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:7" ht="14.6" thickBot="1">
       <c r="A69" s="14"/>
       <c r="B69" s="17"/>
       <c r="C69" s="20"/>
@@ -1340,7 +1442,7 @@
       <c r="F69" s="19"/>
       <c r="G69" s="21"/>
     </row>
-    <row r="70" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:7" ht="14.6" thickBot="1">
       <c r="A70" s="14"/>
       <c r="B70" s="17"/>
       <c r="C70" s="20"/>
@@ -1349,7 +1451,7 @@
       <c r="F70" s="19"/>
       <c r="G70" s="21"/>
     </row>
-    <row r="71" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:7" ht="14.6" thickBot="1">
       <c r="A71" s="14"/>
       <c r="B71" s="17"/>
       <c r="C71" s="20"/>
@@ -1358,7 +1460,7 @@
       <c r="F71" s="19"/>
       <c r="G71" s="21"/>
     </row>
-    <row r="72" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:7" ht="14.6" thickBot="1">
       <c r="A72" s="14"/>
       <c r="B72" s="17"/>
       <c r="C72" s="20"/>
@@ -1367,7 +1469,7 @@
       <c r="F72" s="19"/>
       <c r="G72" s="21"/>
     </row>
-    <row r="73" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:7" ht="14.6" thickBot="1">
       <c r="A73" s="14"/>
       <c r="B73" s="17"/>
       <c r="C73" s="18"/>
@@ -1376,7 +1478,7 @@
       <c r="F73" s="19"/>
       <c r="G73" s="21"/>
     </row>
-    <row r="74" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:7" ht="14.6" thickBot="1">
       <c r="A74" s="14"/>
       <c r="B74" s="17"/>
       <c r="C74" s="18"/>
@@ -1385,7 +1487,7 @@
       <c r="F74" s="19"/>
       <c r="G74" s="21"/>
     </row>
-    <row r="75" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:7" ht="14.6" thickBot="1">
       <c r="A75" s="14"/>
       <c r="B75" s="17"/>
       <c r="C75" s="18"/>
@@ -1394,7 +1496,7 @@
       <c r="F75" s="19"/>
       <c r="G75" s="21"/>
     </row>
-    <row r="76" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:7" ht="14.6" thickBot="1">
       <c r="A76" s="14"/>
       <c r="B76" s="17"/>
       <c r="C76" s="18"/>
@@ -1403,7 +1505,7 @@
       <c r="F76" s="19"/>
       <c r="G76" s="20"/>
     </row>
-    <row r="77" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:7" ht="14.6" thickBot="1">
       <c r="A77" s="14"/>
       <c r="B77" s="17"/>
       <c r="C77" s="18"/>
@@ -1412,7 +1514,7 @@
       <c r="F77" s="19"/>
       <c r="G77" s="20"/>
     </row>
-    <row r="78" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:7" ht="14.6" thickBot="1">
       <c r="A78" s="14"/>
       <c r="B78" s="17"/>
       <c r="C78" s="20"/>
@@ -1421,7 +1523,7 @@
       <c r="F78" s="19"/>
       <c r="G78" s="20"/>
     </row>
-    <row r="79" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="14.6" thickBot="1">
       <c r="A79" s="15"/>
       <c r="B79" s="22"/>
       <c r="C79" s="18"/>
@@ -1430,7 +1532,7 @@
       <c r="F79" s="19"/>
       <c r="G79" s="20"/>
     </row>
-    <row r="80" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="14.6" thickBot="1">
       <c r="A80" s="15"/>
       <c r="B80" s="22"/>
       <c r="C80" s="18"/>
@@ -1439,7 +1541,7 @@
       <c r="F80" s="19"/>
       <c r="G80" s="20"/>
     </row>
-    <row r="81" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="14.6" thickBot="1">
       <c r="A81" s="15"/>
       <c r="B81" s="22"/>
       <c r="C81" s="18"/>
@@ -1448,7 +1550,7 @@
       <c r="F81" s="19"/>
       <c r="G81" s="20"/>
     </row>
-    <row r="82" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="14.6" thickBot="1">
       <c r="A82" s="15"/>
       <c r="B82" s="22"/>
       <c r="C82" s="18"/>
@@ -1457,7 +1559,7 @@
       <c r="F82" s="19"/>
       <c r="G82" s="20"/>
     </row>
-    <row r="83" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:7" ht="14.6" thickBot="1">
       <c r="A83" s="14"/>
       <c r="B83" s="17"/>
       <c r="C83" s="20"/>
@@ -1466,7 +1568,7 @@
       <c r="F83" s="19"/>
       <c r="G83" s="20"/>
     </row>
-    <row r="84" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:7" ht="14.6" thickBot="1">
       <c r="A84" s="14"/>
       <c r="B84" s="17"/>
       <c r="C84" s="18"/>
@@ -1475,7 +1577,7 @@
       <c r="F84" s="19"/>
       <c r="G84" s="20"/>
     </row>
-    <row r="85" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:7" ht="14.6" thickBot="1">
       <c r="A85" s="14"/>
       <c r="B85" s="17"/>
       <c r="C85" s="18"/>
@@ -1484,7 +1586,7 @@
       <c r="F85" s="19"/>
       <c r="G85" s="21"/>
     </row>
-    <row r="86" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:7" ht="14.6" thickBot="1">
       <c r="A86" s="14"/>
       <c r="B86" s="17"/>
       <c r="C86" s="20"/>
@@ -1493,7 +1595,7 @@
       <c r="F86" s="19"/>
       <c r="G86" s="21"/>
     </row>
-    <row r="87" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:7" ht="14.6" thickBot="1">
       <c r="A87" s="14"/>
       <c r="B87" s="17"/>
       <c r="C87" s="20"/>
@@ -1502,7 +1604,7 @@
       <c r="F87" s="19"/>
       <c r="G87" s="21"/>
     </row>
-    <row r="88" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:7" ht="14.6" thickBot="1">
       <c r="A88" s="14"/>
       <c r="B88" s="17"/>
       <c r="C88" s="20"/>
@@ -1511,7 +1613,7 @@
       <c r="F88" s="19"/>
       <c r="G88" s="21"/>
     </row>
-    <row r="89" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:7" ht="14.6" thickBot="1">
       <c r="A89" s="14"/>
       <c r="B89" s="17"/>
       <c r="C89" s="18"/>
@@ -1520,7 +1622,7 @@
       <c r="F89" s="19"/>
       <c r="G89" s="21"/>
     </row>
-    <row r="90" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:7" ht="14.6" thickBot="1">
       <c r="A90" s="14"/>
       <c r="B90" s="17"/>
       <c r="C90" s="18"/>
@@ -1529,7 +1631,7 @@
       <c r="F90" s="19"/>
       <c r="G90" s="21"/>
     </row>
-    <row r="91" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:7" ht="14.6" thickBot="1">
       <c r="A91" s="14"/>
       <c r="B91" s="17"/>
       <c r="C91" s="18"/>
@@ -1538,7 +1640,7 @@
       <c r="F91" s="19"/>
       <c r="G91" s="21"/>
     </row>
-    <row r="92" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:7" ht="14.6" thickBot="1">
       <c r="A92" s="14"/>
       <c r="B92" s="17"/>
       <c r="C92" s="18"/>
@@ -1547,7 +1649,7 @@
       <c r="F92" s="19"/>
       <c r="G92" s="21"/>
     </row>
-    <row r="93" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:7" ht="14.6" thickBot="1">
       <c r="A93" s="14"/>
       <c r="B93" s="17"/>
       <c r="C93" s="20"/>
@@ -1556,7 +1658,7 @@
       <c r="F93" s="19"/>
       <c r="G93" s="21"/>
     </row>
-    <row r="94" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:7" ht="14.6" thickBot="1">
       <c r="A94" s="14"/>
       <c r="B94" s="17"/>
       <c r="C94" s="18"/>
@@ -1565,7 +1667,7 @@
       <c r="F94" s="19"/>
       <c r="G94" s="21"/>
     </row>
-    <row r="95" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:7" ht="14.6" thickBot="1">
       <c r="A95" s="14"/>
       <c r="B95" s="17"/>
       <c r="C95" s="18"/>
@@ -1574,7 +1676,7 @@
       <c r="F95" s="19"/>
       <c r="G95" s="21"/>
     </row>
-    <row r="96" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:7" ht="14.6" thickBot="1">
       <c r="A96" s="14"/>
       <c r="B96" s="17"/>
       <c r="C96" s="18"/>
@@ -1583,7 +1685,7 @@
       <c r="F96" s="19"/>
       <c r="G96" s="20"/>
     </row>
-    <row r="97" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:7" ht="14.6" thickBot="1">
       <c r="A97" s="14"/>
       <c r="B97" s="17"/>
       <c r="C97" s="20"/>
@@ -1592,7 +1694,7 @@
       <c r="F97" s="19"/>
       <c r="G97" s="20"/>
     </row>
-    <row r="98" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:7" ht="14.6" thickBot="1">
       <c r="A98" s="14"/>
       <c r="B98" s="17"/>
       <c r="C98" s="20"/>
@@ -1601,7 +1703,7 @@
       <c r="F98" s="19"/>
       <c r="G98" s="20"/>
     </row>
-    <row r="99" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:7" ht="14.6" thickBot="1">
       <c r="A99" s="14"/>
       <c r="B99" s="17"/>
       <c r="C99" s="18"/>
@@ -1610,7 +1712,7 @@
       <c r="F99" s="19"/>
       <c r="G99" s="21"/>
     </row>
-    <row r="100" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:7" ht="14.6" thickBot="1">
       <c r="A100" s="14"/>
       <c r="B100" s="17"/>
       <c r="C100" s="18"/>
@@ -1619,7 +1721,7 @@
       <c r="F100" s="19"/>
       <c r="G100" s="21"/>
     </row>
-    <row r="101" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" ht="14.6" thickBot="1">
       <c r="A101" s="15"/>
       <c r="B101" s="22"/>
       <c r="C101" s="18"/>
@@ -1628,7 +1730,7 @@
       <c r="F101" s="19"/>
       <c r="G101" s="20"/>
     </row>
-    <row r="102" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:7" ht="14.6" thickBot="1">
       <c r="A102" s="14"/>
       <c r="B102" s="17"/>
       <c r="C102" s="20"/>
@@ -1637,7 +1739,7 @@
       <c r="F102" s="19"/>
       <c r="G102" s="20"/>
     </row>
-    <row r="103" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:7" ht="14.6" thickBot="1">
       <c r="A103" s="14"/>
       <c r="B103" s="17"/>
       <c r="C103" s="18"/>
@@ -1646,7 +1748,7 @@
       <c r="F103" s="19"/>
       <c r="G103" s="21"/>
     </row>
-    <row r="104" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:7" ht="14.6" thickBot="1">
       <c r="A104" s="14"/>
       <c r="B104" s="17"/>
       <c r="C104" s="18"/>
@@ -1655,7 +1757,7 @@
       <c r="F104" s="19"/>
       <c r="G104" s="21"/>
     </row>
-    <row r="105" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="14.6" thickBot="1">
       <c r="A105" s="15"/>
       <c r="B105" s="22"/>
       <c r="C105" s="18"/>
@@ -1664,7 +1766,7 @@
       <c r="F105" s="19"/>
       <c r="G105" s="21"/>
     </row>
-    <row r="106" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:7" ht="14.6" thickBot="1">
       <c r="A106" s="8"/>
       <c r="B106" s="9"/>
       <c r="C106" s="1"/>
@@ -1673,7 +1775,7 @@
       <c r="F106" s="3"/>
       <c r="G106" s="2"/>
     </row>
-    <row r="107" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:7" ht="14.6" thickBot="1">
       <c r="A107" s="8"/>
       <c r="B107" s="9"/>
       <c r="C107" s="1"/>
@@ -1682,7 +1784,7 @@
       <c r="F107" s="3"/>
       <c r="G107" s="4"/>
     </row>
-    <row r="108" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:7" ht="14.6" thickBot="1">
       <c r="A108" s="11"/>
       <c r="B108" s="12"/>
       <c r="C108" s="1"/>
@@ -1691,7 +1793,7 @@
       <c r="F108" s="3"/>
       <c r="G108" s="4"/>
     </row>
-    <row r="109" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:7" ht="14.6" thickBot="1">
       <c r="A109" s="8"/>
       <c r="B109" s="9"/>
       <c r="C109" s="1"/>
@@ -1700,7 +1802,7 @@
       <c r="F109" s="3"/>
       <c r="G109" s="2"/>
     </row>
-    <row r="110" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:7" ht="14.6" thickBot="1">
       <c r="A110" s="11"/>
       <c r="B110" s="12"/>
       <c r="C110" s="1"/>
@@ -1709,7 +1811,7 @@
       <c r="F110" s="3"/>
       <c r="G110" s="2"/>
     </row>
-    <row r="111" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:7" ht="14.6" thickBot="1">
       <c r="A111" s="8"/>
       <c r="B111" s="9"/>
       <c r="C111" s="1"/>
@@ -1718,7 +1820,7 @@
       <c r="F111" s="3"/>
       <c r="G111" s="2"/>
     </row>
-    <row r="112" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:7" ht="14.6" thickBot="1">
       <c r="A112" s="11"/>
       <c r="B112" s="12"/>
       <c r="C112" s="2"/>
@@ -1727,7 +1829,7 @@
       <c r="F112" s="3"/>
       <c r="G112" s="4"/>
     </row>
-    <row r="113" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:7" ht="14.6" thickBot="1">
       <c r="A113" s="8"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -1736,7 +1838,7 @@
       <c r="F113" s="3"/>
       <c r="G113" s="4"/>
     </row>
-    <row r="114" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:7" ht="14.6" thickBot="1">
       <c r="A114" s="8"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -1745,7 +1847,7 @@
       <c r="F114" s="3"/>
       <c r="G114" s="2"/>
     </row>
-    <row r="115" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:7" ht="14.6" thickBot="1">
       <c r="A115" s="8"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -1754,7 +1856,7 @@
       <c r="F115" s="3"/>
       <c r="G115" s="4"/>
     </row>
-    <row r="116" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:7" ht="14.6" thickBot="1">
       <c r="A116" s="11"/>
       <c r="B116" s="12"/>
       <c r="C116" s="2"/>
@@ -1763,7 +1865,7 @@
       <c r="F116" s="3"/>
       <c r="G116" s="4"/>
     </row>
-    <row r="117" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:7" ht="14.6" thickBot="1">
       <c r="A117" s="11"/>
       <c r="B117" s="12"/>
       <c r="C117" s="2"/>
@@ -1772,7 +1874,7 @@
       <c r="F117" s="3"/>
       <c r="G117" s="2"/>
     </row>
-    <row r="118" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:7" ht="14.6" thickBot="1">
       <c r="A118" s="11"/>
       <c r="B118" s="12"/>
       <c r="C118" s="1"/>
@@ -1781,7 +1883,7 @@
       <c r="F118" s="3"/>
       <c r="G118" s="4"/>
     </row>
-    <row r="119" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:7" ht="14.6" thickBot="1">
       <c r="A119" s="11"/>
       <c r="B119" s="12"/>
       <c r="C119" s="2"/>
@@ -1790,7 +1892,7 @@
       <c r="F119" s="3"/>
       <c r="G119" s="4"/>
     </row>
-    <row r="120" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:7" ht="14.6" thickBot="1">
       <c r="A120" s="11"/>
       <c r="B120" s="12"/>
       <c r="C120" s="2"/>
@@ -1799,7 +1901,7 @@
       <c r="F120" s="3"/>
       <c r="G120" s="2"/>
     </row>
-    <row r="121" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:7" ht="14.6" thickBot="1">
       <c r="A121" s="11"/>
       <c r="B121" s="12"/>
       <c r="C121" s="2"/>
@@ -1808,7 +1910,7 @@
       <c r="F121" s="3"/>
       <c r="G121" s="4"/>
     </row>
-    <row r="122" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:7" ht="14.6" thickBot="1">
       <c r="A122" s="11"/>
       <c r="B122" s="12"/>
       <c r="C122" s="1"/>
@@ -1817,7 +1919,7 @@
       <c r="F122" s="3"/>
       <c r="G122" s="4"/>
     </row>
-    <row r="123" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:7" ht="14.6" thickBot="1">
       <c r="A123" s="11"/>
       <c r="B123" s="12"/>
       <c r="C123" s="2"/>
@@ -1826,7 +1928,7 @@
       <c r="F123" s="3"/>
       <c r="G123" s="4"/>
     </row>
-    <row r="124" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:7" ht="14.6" thickBot="1">
       <c r="A124" s="8"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -1835,7 +1937,7 @@
       <c r="F124" s="3"/>
       <c r="G124" s="2"/>
     </row>
-    <row r="125" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:7" ht="14.6" thickBot="1">
       <c r="A125" s="11"/>
       <c r="B125" s="12"/>
       <c r="C125" s="1"/>
@@ -1844,7 +1946,7 @@
       <c r="F125" s="3"/>
       <c r="G125" s="4"/>
     </row>
-    <row r="126" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:7" ht="14.6" thickBot="1">
       <c r="A126" s="8"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -1853,7 +1955,7 @@
       <c r="F126" s="3"/>
       <c r="G126" s="4"/>
     </row>
-    <row r="127" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:7" ht="14.6" thickBot="1">
       <c r="A127" s="8"/>
       <c r="B127" s="9"/>
       <c r="C127" s="1"/>
@@ -1862,7 +1964,7 @@
       <c r="F127" s="3"/>
       <c r="G127" s="4"/>
     </row>
-    <row r="128" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:7" ht="14.6" thickBot="1">
       <c r="A128" s="8"/>
       <c r="B128" s="9"/>
       <c r="C128" s="1"/>
@@ -1871,7 +1973,7 @@
       <c r="F128" s="3"/>
       <c r="G128" s="4"/>
     </row>
-    <row r="129" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:7" ht="14.6" thickBot="1">
       <c r="A129" s="8"/>
       <c r="B129" s="9"/>
       <c r="C129" s="1"/>
@@ -1880,7 +1982,7 @@
       <c r="F129" s="3"/>
       <c r="G129" s="4"/>
     </row>
-    <row r="130" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:7" ht="14.6" thickBot="1">
       <c r="A130" s="11"/>
       <c r="B130" s="12"/>
       <c r="C130" s="1"/>
@@ -1889,7 +1991,7 @@
       <c r="F130" s="3"/>
       <c r="G130" s="4"/>
     </row>
-    <row r="131" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:7" ht="14.6" thickBot="1">
       <c r="A131" s="8"/>
       <c r="B131" s="9"/>
       <c r="C131" s="1"/>
@@ -1898,7 +2000,7 @@
       <c r="F131" s="3"/>
       <c r="G131" s="4"/>
     </row>
-    <row r="132" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:7" ht="14.6" thickBot="1">
       <c r="A132" s="11"/>
       <c r="B132" s="12"/>
       <c r="C132" s="2"/>
@@ -1907,7 +2009,7 @@
       <c r="F132" s="5"/>
       <c r="G132" s="2"/>
     </row>
-    <row r="133" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:7" ht="14.6" thickBot="1">
       <c r="A133" s="8"/>
       <c r="B133" s="9"/>
       <c r="C133" s="1"/>
@@ -1916,7 +2018,7 @@
       <c r="F133" s="3"/>
       <c r="G133" s="4"/>
     </row>
-    <row r="134" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:7" ht="14.6" thickBot="1">
       <c r="A134" s="8"/>
       <c r="B134" s="9"/>
       <c r="C134" s="1"/>
@@ -1925,7 +2027,7 @@
       <c r="F134" s="3"/>
       <c r="G134" s="4"/>
     </row>
-    <row r="135" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:7" ht="14.6" thickBot="1">
       <c r="A135" s="8"/>
       <c r="B135" s="9"/>
       <c r="C135" s="1"/>
@@ -1934,7 +2036,7 @@
       <c r="F135" s="3"/>
       <c r="G135" s="4"/>
     </row>
-    <row r="136" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:7" ht="14.6" thickBot="1">
       <c r="A136" s="8"/>
       <c r="B136" s="9"/>
       <c r="C136" s="1"/>
@@ -1943,7 +2045,7 @@
       <c r="F136" s="3"/>
       <c r="G136" s="4"/>
     </row>
-    <row r="137" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:7" ht="14.6" thickBot="1">
       <c r="A137" s="8"/>
       <c r="B137" s="9"/>
       <c r="C137" s="1"/>
@@ -1952,7 +2054,7 @@
       <c r="F137" s="3"/>
       <c r="G137" s="4"/>
     </row>
-    <row r="138" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:7" ht="14.6" thickBot="1">
       <c r="A138" s="8"/>
       <c r="B138" s="9"/>
       <c r="C138" s="1"/>
@@ -1961,7 +2063,7 @@
       <c r="F138" s="3"/>
       <c r="G138" s="4"/>
     </row>
-    <row r="139" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:7" ht="14.6" thickBot="1">
       <c r="A139" s="8"/>
       <c r="B139" s="9"/>
       <c r="C139" s="1"/>
@@ -1970,7 +2072,7 @@
       <c r="F139" s="3"/>
       <c r="G139" s="4"/>
     </row>
-    <row r="140" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:7" ht="14.6" thickBot="1">
       <c r="A140" s="8"/>
       <c r="B140" s="9"/>
       <c r="C140" s="1"/>
@@ -1979,7 +2081,7 @@
       <c r="F140" s="3"/>
       <c r="G140" s="4"/>
     </row>
-    <row r="141" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:7" ht="14.6" thickBot="1">
       <c r="A141" s="8"/>
       <c r="B141" s="9"/>
       <c r="C141" s="1"/>
@@ -1988,7 +2090,7 @@
       <c r="F141" s="3"/>
       <c r="G141" s="4"/>
     </row>
-    <row r="142" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:7" ht="14.6" thickBot="1">
       <c r="A142" s="8"/>
       <c r="B142" s="9"/>
       <c r="C142" s="1"/>
@@ -1997,7 +2099,7 @@
       <c r="F142" s="3"/>
       <c r="G142" s="4"/>
     </row>
-    <row r="143" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:7" ht="14.6" thickBot="1">
       <c r="A143" s="8"/>
       <c r="B143" s="9"/>
       <c r="C143" s="1"/>
@@ -2006,7 +2108,7 @@
       <c r="F143" s="3"/>
       <c r="G143" s="4"/>
     </row>
-    <row r="144" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:7" ht="14.6" thickBot="1">
       <c r="A144" s="8"/>
       <c r="B144" s="9"/>
       <c r="C144" s="1"/>
@@ -2015,7 +2117,7 @@
       <c r="F144" s="3"/>
       <c r="G144" s="4"/>
     </row>
-    <row r="145" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:7" ht="14.6" thickBot="1">
       <c r="A145" s="11"/>
       <c r="B145" s="12"/>
       <c r="C145" s="1"/>
@@ -2024,7 +2126,7 @@
       <c r="F145" s="3"/>
       <c r="G145" s="4"/>
     </row>
-    <row r="146" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" ht="14.6" thickBot="1">
       <c r="A146" s="8"/>
       <c r="B146" s="9"/>
       <c r="C146" s="1"/>
@@ -2033,7 +2135,7 @@
       <c r="F146" s="3"/>
       <c r="G146" s="4"/>
     </row>
-    <row r="147" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" ht="14.6" thickBot="1">
       <c r="A147" s="8"/>
       <c r="B147" s="9"/>
       <c r="C147" s="1"/>
@@ -2042,7 +2144,7 @@
       <c r="F147" s="3"/>
       <c r="G147" s="4"/>
     </row>
-    <row r="148" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:7" ht="14.6" thickBot="1">
       <c r="A148" s="8"/>
       <c r="B148" s="9"/>
       <c r="C148" s="1"/>
@@ -2051,7 +2153,7 @@
       <c r="F148" s="3"/>
       <c r="G148" s="4"/>
     </row>
-    <row r="149" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" ht="14.6" thickBot="1">
       <c r="A149" s="8"/>
       <c r="B149" s="9"/>
       <c r="C149" s="1"/>
@@ -2060,7 +2162,7 @@
       <c r="F149" s="3"/>
       <c r="G149" s="4"/>
     </row>
-    <row r="150" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:7" ht="14.6" thickBot="1">
       <c r="A150" s="11"/>
       <c r="B150" s="12"/>
       <c r="C150" s="1"/>
@@ -2069,7 +2171,7 @@
       <c r="F150" s="3"/>
       <c r="G150" s="4"/>
     </row>
-    <row r="151" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:7" ht="14.6" thickBot="1">
       <c r="A151" s="8"/>
       <c r="B151" s="9"/>
       <c r="C151" s="1"/>
@@ -2078,7 +2180,7 @@
       <c r="F151" s="3"/>
       <c r="G151" s="4"/>
     </row>
-    <row r="152" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:7" ht="14.6" thickBot="1">
       <c r="A152" s="8"/>
       <c r="B152" s="9"/>
       <c r="C152" s="1"/>
@@ -2087,7 +2189,7 @@
       <c r="F152" s="3"/>
       <c r="G152" s="4"/>
     </row>
-    <row r="153" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:7" ht="14.6" thickBot="1">
       <c r="A153" s="11"/>
       <c r="B153" s="12"/>
       <c r="C153" s="2"/>
@@ -2096,7 +2198,7 @@
       <c r="F153" s="3"/>
       <c r="G153" s="4"/>
     </row>
-    <row r="154" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:7" ht="14.6" thickBot="1">
       <c r="A154" s="11"/>
       <c r="B154" s="12"/>
       <c r="C154" s="2"/>
@@ -2105,7 +2207,7 @@
       <c r="F154" s="3"/>
       <c r="G154" s="4"/>
     </row>
-    <row r="155" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:7" ht="14.6" thickBot="1">
       <c r="A155" s="11"/>
       <c r="B155" s="12"/>
       <c r="C155" s="1"/>
@@ -2114,7 +2216,7 @@
       <c r="F155" s="3"/>
       <c r="G155" s="4"/>
     </row>
-    <row r="156" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:7" ht="14.6" thickBot="1">
       <c r="A156" s="8"/>
       <c r="B156" s="9"/>
       <c r="C156" s="1"/>
@@ -2123,7 +2225,7 @@
       <c r="F156" s="3"/>
       <c r="G156" s="4"/>
     </row>
-    <row r="157" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:7" ht="14.6" thickBot="1">
       <c r="A157" s="8"/>
       <c r="B157" s="9"/>
       <c r="C157" s="1"/>
@@ -2132,7 +2234,7 @@
       <c r="F157" s="3"/>
       <c r="G157" s="4"/>
     </row>
-    <row r="158" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:7" ht="14.6" thickBot="1">
       <c r="A158" s="8"/>
       <c r="B158" s="9"/>
       <c r="C158" s="1"/>
@@ -2141,7 +2243,7 @@
       <c r="F158" s="3"/>
       <c r="G158" s="4"/>
     </row>
-    <row r="159" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:7" ht="14.6" thickBot="1">
       <c r="A159" s="8"/>
       <c r="B159" s="9"/>
       <c r="C159" s="1"/>
@@ -2150,7 +2252,7 @@
       <c r="F159" s="3"/>
       <c r="G159" s="4"/>
     </row>
-    <row r="160" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:7" ht="14.6" thickBot="1">
       <c r="A160" s="8"/>
       <c r="B160" s="9"/>
       <c r="C160" s="1"/>
@@ -2159,7 +2261,7 @@
       <c r="F160" s="5"/>
       <c r="G160" s="4"/>
     </row>
-    <row r="161" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:7" ht="14.6" thickBot="1">
       <c r="A161" s="8"/>
       <c r="B161" s="9"/>
       <c r="C161" s="1"/>
@@ -2168,7 +2270,7 @@
       <c r="F161" s="5"/>
       <c r="G161" s="4"/>
     </row>
-    <row r="162" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:7" ht="14.6" thickBot="1">
       <c r="A162" s="8"/>
       <c r="B162" s="9"/>
       <c r="C162" s="1"/>
@@ -2177,7 +2279,7 @@
       <c r="F162" s="5"/>
       <c r="G162" s="4"/>
     </row>
-    <row r="163" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:7" ht="14.6" thickBot="1">
       <c r="A163" s="8"/>
       <c r="B163" s="9"/>
       <c r="C163" s="1"/>
@@ -2186,7 +2288,7 @@
       <c r="F163" s="5"/>
       <c r="G163" s="4"/>
     </row>
-    <row r="164" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:7" ht="14.6" thickBot="1">
       <c r="A164" s="8"/>
       <c r="B164" s="9"/>
       <c r="C164" s="1"/>
@@ -2195,7 +2297,7 @@
       <c r="F164" s="3"/>
       <c r="G164" s="4"/>
     </row>
-    <row r="165" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:7" ht="14.6" thickBot="1">
       <c r="A165" s="8"/>
       <c r="B165" s="9"/>
       <c r="C165" s="1"/>
@@ -2204,7 +2306,7 @@
       <c r="F165" s="3"/>
       <c r="G165" s="4"/>
     </row>
-    <row r="166" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:7" ht="14.6" thickBot="1">
       <c r="A166" s="8"/>
       <c r="B166" s="9"/>
       <c r="C166" s="1"/>
@@ -2213,7 +2315,7 @@
       <c r="F166" s="3"/>
       <c r="G166" s="4"/>
     </row>
-    <row r="167" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:7" ht="14.6" thickBot="1">
       <c r="A167" s="8"/>
       <c r="B167" s="9"/>
       <c r="C167" s="1"/>
@@ -2222,7 +2324,7 @@
       <c r="F167" s="3"/>
       <c r="G167" s="4"/>
     </row>
-    <row r="168" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:7" ht="14.6" thickBot="1">
       <c r="A168" s="8"/>
       <c r="B168" s="9"/>
       <c r="C168" s="1"/>
@@ -2231,7 +2333,7 @@
       <c r="F168" s="3"/>
       <c r="G168" s="4"/>
     </row>
-    <row r="169" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:7" ht="14.6" thickBot="1">
       <c r="A169" s="8"/>
       <c r="B169" s="9"/>
       <c r="C169" s="1"/>
@@ -2240,7 +2342,7 @@
       <c r="F169" s="3"/>
       <c r="G169" s="4"/>
     </row>
-    <row r="170" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:7" ht="14.6" thickBot="1">
       <c r="A170" s="8"/>
       <c r="B170" s="9"/>
       <c r="C170" s="1"/>
@@ -2249,7 +2351,7 @@
       <c r="F170" s="3"/>
       <c r="G170" s="4"/>
     </row>
-    <row r="171" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:7" ht="14.6" thickBot="1">
       <c r="A171" s="8"/>
       <c r="B171" s="9"/>
       <c r="C171" s="1"/>
@@ -2258,7 +2360,7 @@
       <c r="F171" s="3"/>
       <c r="G171" s="4"/>
     </row>
-    <row r="172" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:7" ht="14.6" thickBot="1">
       <c r="A172" s="8"/>
       <c r="B172" s="9"/>
       <c r="C172" s="1"/>
@@ -2267,7 +2369,7 @@
       <c r="F172" s="3"/>
       <c r="G172" s="4"/>
     </row>
-    <row r="173" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:7" ht="14.6" thickBot="1">
       <c r="A173" s="8"/>
       <c r="B173" s="9"/>
       <c r="C173" s="1"/>
@@ -2276,7 +2378,7 @@
       <c r="F173" s="3"/>
       <c r="G173" s="4"/>
     </row>
-    <row r="174" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:7" ht="14.6" thickBot="1">
       <c r="A174" s="8"/>
       <c r="B174" s="9"/>
       <c r="C174" s="1"/>
@@ -2285,7 +2387,7 @@
       <c r="F174" s="3"/>
       <c r="G174" s="4"/>
     </row>
-    <row r="175" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:7" ht="14.6" thickBot="1">
       <c r="A175" s="8"/>
       <c r="B175" s="9"/>
       <c r="C175" s="1"/>
@@ -2294,7 +2396,7 @@
       <c r="F175" s="3"/>
       <c r="G175" s="4"/>
     </row>
-    <row r="176" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:7" ht="14.6" thickBot="1">
       <c r="A176" s="11"/>
       <c r="B176" s="12"/>
       <c r="C176" s="1"/>
@@ -2303,7 +2405,7 @@
       <c r="F176" s="3"/>
       <c r="G176" s="4"/>
     </row>
-    <row r="177" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" ht="14.6" thickBot="1">
       <c r="A177" s="8"/>
       <c r="B177" s="9"/>
       <c r="C177" s="1"/>
@@ -2312,7 +2414,7 @@
       <c r="F177" s="3"/>
       <c r="G177" s="4"/>
     </row>
-    <row r="178" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" ht="14.6" thickBot="1">
       <c r="A178" s="8"/>
       <c r="B178" s="9"/>
       <c r="C178" s="1"/>
@@ -2321,7 +2423,7 @@
       <c r="F178" s="3"/>
       <c r="G178" s="4"/>
     </row>
-    <row r="179" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:7" ht="14.6" thickBot="1">
       <c r="A179" s="8"/>
       <c r="B179" s="9"/>
       <c r="C179" s="1"/>
@@ -2330,7 +2432,7 @@
       <c r="F179" s="3"/>
       <c r="G179" s="4"/>
     </row>
-    <row r="180" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" ht="14.6" thickBot="1">
       <c r="A180" s="8"/>
       <c r="B180" s="9"/>
       <c r="C180" s="1"/>
@@ -2339,7 +2441,7 @@
       <c r="F180" s="3"/>
       <c r="G180" s="4"/>
     </row>
-    <row r="181" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:7" ht="14.6" thickBot="1">
       <c r="A181" s="11"/>
       <c r="B181" s="12"/>
       <c r="C181" s="1"/>
@@ -2348,7 +2450,7 @@
       <c r="F181" s="3"/>
       <c r="G181" s="4"/>
     </row>
-    <row r="182" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:7" ht="14.6" thickBot="1">
       <c r="A182" s="8"/>
       <c r="B182" s="9"/>
       <c r="C182" s="1"/>
@@ -2357,7 +2459,7 @@
       <c r="F182" s="3"/>
       <c r="G182" s="4"/>
     </row>
-    <row r="183" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:7" ht="14.6" thickBot="1">
       <c r="A183" s="8"/>
       <c r="B183" s="9"/>
       <c r="C183" s="1"/>
@@ -2366,7 +2468,7 @@
       <c r="F183" s="3"/>
       <c r="G183" s="4"/>
     </row>
-    <row r="184" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:7" ht="14.6" thickBot="1">
       <c r="A184" s="11"/>
       <c r="B184" s="12"/>
       <c r="C184" s="2"/>
@@ -2375,7 +2477,7 @@
       <c r="F184" s="3"/>
       <c r="G184" s="4"/>
     </row>
-    <row r="185" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:7" ht="14.6" thickBot="1">
       <c r="A185" s="11"/>
       <c r="B185" s="12"/>
       <c r="C185" s="2"/>
@@ -2384,7 +2486,7 @@
       <c r="F185" s="3"/>
       <c r="G185" s="4"/>
     </row>
-    <row r="186" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:7" ht="14.6" thickBot="1">
       <c r="A186" s="11"/>
       <c r="B186" s="12"/>
       <c r="C186" s="1"/>
@@ -2393,7 +2495,7 @@
       <c r="F186" s="3"/>
       <c r="G186" s="4"/>
     </row>
-    <row r="187" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:7" ht="14.6" thickBot="1">
       <c r="A187" s="8"/>
       <c r="B187" s="9"/>
       <c r="C187" s="1"/>
@@ -2402,7 +2504,7 @@
       <c r="F187" s="3"/>
       <c r="G187" s="4"/>
     </row>
-    <row r="188" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:7" ht="14.6" thickBot="1">
       <c r="A188" s="8"/>
       <c r="B188" s="9"/>
       <c r="C188" s="1"/>
@@ -2411,7 +2513,7 @@
       <c r="F188" s="3"/>
       <c r="G188" s="4"/>
     </row>
-    <row r="189" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:7" ht="14.6" thickBot="1">
       <c r="A189" s="8"/>
       <c r="B189" s="9"/>
       <c r="C189" s="1"/>
@@ -2420,7 +2522,7 @@
       <c r="F189" s="3"/>
       <c r="G189" s="4"/>
     </row>
-    <row r="190" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:7" ht="14.6" thickBot="1">
       <c r="A190" s="8"/>
       <c r="B190" s="9"/>
       <c r="C190" s="1"/>
@@ -2429,7 +2531,7 @@
       <c r="F190" s="3"/>
       <c r="G190" s="4"/>
     </row>
-    <row r="191" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:7" ht="14.6" thickBot="1">
       <c r="A191" s="8"/>
       <c r="B191" s="9"/>
       <c r="C191" s="1"/>
@@ -2438,7 +2540,7 @@
       <c r="F191" s="5"/>
       <c r="G191" s="4"/>
     </row>
-    <row r="192" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:7" ht="14.6" thickBot="1">
       <c r="A192" s="8"/>
       <c r="B192" s="9"/>
       <c r="C192" s="1"/>
@@ -2447,7 +2549,7 @@
       <c r="F192" s="5"/>
       <c r="G192" s="4"/>
     </row>
-    <row r="193" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:7" ht="14.6" thickBot="1">
       <c r="A193" s="8"/>
       <c r="B193" s="9"/>
       <c r="C193" s="1"/>
@@ -2456,7 +2558,7 @@
       <c r="F193" s="5"/>
       <c r="G193" s="4"/>
     </row>
-    <row r="194" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:7" ht="14.6" thickBot="1">
       <c r="A194" s="8"/>
       <c r="B194" s="9"/>
       <c r="C194" s="1"/>
